--- a/Thesis_TSSP_NEW_M2_Results_25_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_25_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1800.7830 sec</t>
+          <t>1801.1770 sec</t>
         </is>
       </c>
     </row>
